--- a/backend/relacao_pessoas.xlsx
+++ b/backend/relacao_pessoas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2866"/>
+  <dimension ref="A1:E2867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2056,7 +2056,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2916,7 +2916,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3233,7 +3233,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3347,7 +3347,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3537,7 +3537,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3689,7 +3689,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3708,7 +3708,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3803,7 +3803,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3879,7 +3879,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3917,7 +3917,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3993,7 +3993,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4069,7 +4069,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4107,7 +4107,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4168,7 +4168,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4256,7 +4256,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4774,7 +4774,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4812,7 +4812,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5021,7 +5021,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5538,7 +5538,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5557,7 +5557,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5664,7 +5664,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5798,7 +5798,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6028,7 +6028,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6055,7 +6055,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6520,7 +6520,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6596,7 +6596,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6615,7 +6615,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6881,7 +6881,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6957,7 +6957,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6995,7 +6995,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7068,7 +7068,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7110,7 +7110,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7171,7 +7171,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7263,7 +7263,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7451,7 +7451,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7958,7 +7958,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7977,7 +7977,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8073,7 +8073,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8188,7 +8188,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8379,7 +8379,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8436,7 +8436,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8645,7 +8645,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8778,7 +8778,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8873,7 +8873,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -8930,7 +8930,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -8987,7 +8987,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -9025,7 +9025,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -9044,7 +9044,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -9132,7 +9132,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -9434,7 +9434,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9645,7 +9645,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -10056,7 +10056,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -10209,7 +10209,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -10378,7 +10378,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -10470,7 +10470,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -10512,7 +10512,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -10626,7 +10626,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -10702,7 +10702,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -10740,7 +10740,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -10797,7 +10797,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -10930,7 +10930,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -10968,7 +10968,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -11006,7 +11006,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -11082,7 +11082,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -11139,7 +11139,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -11522,7 +11522,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -11568,7 +11568,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -11798,7 +11798,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -11990,7 +11990,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -12432,7 +12432,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -12498,7 +12498,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -12593,7 +12593,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -12669,7 +12669,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -12707,7 +12707,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -12764,7 +12764,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -12802,7 +12802,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -12821,7 +12821,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -12859,7 +12859,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -12897,7 +12897,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -12954,7 +12954,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -12973,7 +12973,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -13030,7 +13030,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -13087,7 +13087,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -13106,7 +13106,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -13144,7 +13144,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -13390,7 +13390,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -13793,7 +13793,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -14616,7 +14616,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -14789,7 +14789,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -14808,7 +14808,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -14896,7 +14896,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -15342,7 +15342,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -15361,7 +15361,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -15399,7 +15399,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -15456,7 +15456,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -15475,7 +15475,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -15551,7 +15551,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -15570,7 +15570,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -15608,7 +15608,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -15646,7 +15646,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -15703,7 +15703,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -15741,7 +15741,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -15817,7 +15817,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -15836,7 +15836,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -15855,7 +15855,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -15874,7 +15874,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -16350,7 +16350,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -16423,7 +16423,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -16568,7 +16568,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -16587,7 +16587,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -16625,7 +16625,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -16701,7 +16701,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -16739,7 +16739,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -17115,7 +17115,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -17249,7 +17249,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -17306,7 +17306,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -17325,7 +17325,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -17455,7 +17455,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -17593,7 +17593,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -17969,7 +17969,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -18795,7 +18795,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -18902,7 +18902,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -18921,7 +18921,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -19021,7 +19021,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -19273,7 +19273,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -19311,7 +19311,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -19349,7 +19349,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -19387,7 +19387,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -19406,7 +19406,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -19463,7 +19463,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -19482,7 +19482,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -19558,7 +19558,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -19672,7 +19672,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -19710,7 +19710,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -19748,7 +19748,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -19805,7 +19805,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -19824,7 +19824,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -19843,7 +19843,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -19862,7 +19862,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -19881,7 +19881,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -19957,7 +19957,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -20122,7 +20122,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -20513,7 +20513,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -20589,7 +20589,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -20627,7 +20627,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -20703,7 +20703,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -20722,7 +20722,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -20760,7 +20760,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -21189,7 +21189,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -21235,7 +21235,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -21561,7 +21561,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -21630,7 +21630,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -21987,7 +21987,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -22025,7 +22025,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -22090,7 +22090,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -22386,7 +22386,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -22674,7 +22674,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -22793,7 +22793,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
@@ -23084,7 +23084,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -23145,7 +23145,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -23241,7 +23241,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -23455,7 +23455,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
@@ -23474,7 +23474,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -23512,7 +23512,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -23531,7 +23531,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
@@ -23569,7 +23569,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
@@ -23626,7 +23626,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -23721,7 +23721,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -23900,7 +23900,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -23919,7 +23919,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
@@ -23938,7 +23938,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -23957,7 +23957,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -24071,7 +24071,7 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
@@ -24185,7 +24185,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
@@ -24299,7 +24299,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
@@ -24413,7 +24413,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -24432,7 +24432,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -24527,7 +24527,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
@@ -24546,7 +24546,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -24607,7 +24607,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
@@ -24976,7 +24976,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
@@ -25267,7 +25267,7 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
@@ -25359,7 +25359,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
@@ -25616,7 +25616,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
@@ -25981,7 +25981,7 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
@@ -26250,7 +26250,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
@@ -26296,7 +26296,7 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
@@ -26315,7 +26315,7 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
@@ -26334,7 +26334,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
@@ -27044,7 +27044,7 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
@@ -27078,7 +27078,7 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
@@ -27173,7 +27173,7 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
@@ -27192,7 +27192,7 @@
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1216" t="inlineStr">
@@ -27211,7 +27211,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
@@ -27287,7 +27287,7 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
@@ -27325,7 +27325,7 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
@@ -27382,7 +27382,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
@@ -27420,7 +27420,7 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
@@ -27439,7 +27439,7 @@
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1229" t="inlineStr">
@@ -27534,7 +27534,7 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
@@ -27553,7 +27553,7 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -27572,7 +27572,7 @@
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
@@ -27629,7 +27629,7 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
@@ -27762,7 +27762,7 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
@@ -27781,7 +27781,7 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
@@ -27800,7 +27800,7 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
@@ -27857,7 +27857,7 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
@@ -27876,7 +27876,7 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
@@ -27895,7 +27895,7 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
@@ -28113,7 +28113,7 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1263" t="inlineStr">
@@ -28259,7 +28259,7 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
@@ -28301,7 +28301,7 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
@@ -28489,7 +28489,7 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
@@ -28724,7 +28724,7 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
@@ -28838,7 +28838,7 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
@@ -28933,7 +28933,7 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
@@ -28990,7 +28990,7 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
@@ -29086,7 +29086,7 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
@@ -29205,7 +29205,7 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
@@ -29224,7 +29224,7 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
@@ -29339,7 +29339,7 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
@@ -29381,7 +29381,7 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
@@ -29527,7 +29527,7 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
@@ -29581,7 +29581,7 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
@@ -29627,7 +29627,7 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
@@ -29968,7 +29968,7 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
@@ -30022,7 +30022,7 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
@@ -30068,7 +30068,7 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
@@ -30217,7 +30217,7 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
@@ -30255,7 +30255,7 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
@@ -30350,7 +30350,7 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
@@ -30369,7 +30369,7 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
@@ -30407,7 +30407,7 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
@@ -30445,7 +30445,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
@@ -30521,7 +30521,7 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
@@ -30663,7 +30663,7 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
@@ -30736,7 +30736,7 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
@@ -30755,7 +30755,7 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
@@ -30774,7 +30774,7 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
@@ -31058,7 +31058,7 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
@@ -31273,7 +31273,7 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
@@ -31319,7 +31319,7 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
@@ -31476,7 +31476,7 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
@@ -31545,7 +31545,7 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
@@ -31817,7 +31817,7 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
@@ -32181,7 +32181,7 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
@@ -32304,7 +32304,7 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
@@ -32461,7 +32461,7 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
@@ -32480,7 +32480,7 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -32591,7 +32591,7 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
@@ -32610,7 +32610,7 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
@@ -32648,7 +32648,7 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
@@ -32781,7 +32781,7 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
@@ -32857,7 +32857,7 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
@@ -32895,7 +32895,7 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -32933,7 +32933,7 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
@@ -32952,7 +32952,7 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
@@ -33047,7 +33047,7 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
@@ -33104,7 +33104,7 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
@@ -33123,7 +33123,7 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
@@ -33142,7 +33142,7 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
@@ -33218,7 +33218,7 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
@@ -33237,7 +33237,7 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
@@ -33294,7 +33294,7 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
@@ -33351,7 +33351,7 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
@@ -33389,7 +33389,7 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
@@ -33408,7 +33408,7 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
@@ -33446,7 +33446,7 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
@@ -33522,7 +33522,7 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
@@ -33541,7 +33541,7 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
@@ -33617,7 +33617,7 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
@@ -33678,7 +33678,7 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
@@ -33754,7 +33754,7 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -33830,7 +33830,7 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
@@ -33849,7 +33849,7 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
@@ -33887,7 +33887,7 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
@@ -33925,7 +33925,7 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
@@ -33963,7 +33963,7 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
@@ -33982,7 +33982,7 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
@@ -34039,7 +34039,7 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
@@ -34189,7 +34189,7 @@
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
@@ -34254,7 +34254,7 @@
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
@@ -34369,7 +34369,7 @@
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
@@ -34407,7 +34407,7 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
@@ -34676,7 +34676,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -34741,7 +34741,7 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -34760,7 +34760,7 @@
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
@@ -34844,7 +34844,7 @@
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
@@ -34920,7 +34920,7 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -34958,7 +34958,7 @@
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
@@ -34997,7 +34997,7 @@
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1581" t="inlineStr">
@@ -35054,7 +35054,7 @@
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1584" t="inlineStr">
@@ -35073,7 +35073,7 @@
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
@@ -35111,7 +35111,7 @@
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
@@ -35149,7 +35149,7 @@
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -35187,7 +35187,7 @@
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -35225,7 +35225,7 @@
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
@@ -35244,7 +35244,7 @@
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
@@ -35801,7 +35801,7 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -35966,7 +35966,7 @@
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
@@ -36089,7 +36089,7 @@
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1629" t="inlineStr">
@@ -36246,7 +36246,7 @@
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1636" t="inlineStr">
@@ -36265,7 +36265,7 @@
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1637" t="inlineStr">
@@ -36361,7 +36361,7 @@
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1641" t="inlineStr">
@@ -36422,7 +36422,7 @@
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1644" t="inlineStr">
@@ -36441,7 +36441,7 @@
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1645" t="inlineStr">
@@ -36479,7 +36479,7 @@
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1647" t="inlineStr">
@@ -36498,7 +36498,7 @@
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1648" t="inlineStr">
@@ -36517,7 +36517,7 @@
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1649" t="inlineStr">
@@ -36688,7 +36688,7 @@
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1658" t="inlineStr">
@@ -36726,7 +36726,7 @@
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1660" t="inlineStr">
@@ -36745,7 +36745,7 @@
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1661" t="inlineStr">
@@ -36840,7 +36840,7 @@
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
@@ -36935,7 +36935,7 @@
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1671" t="inlineStr">
@@ -36954,7 +36954,7 @@
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
@@ -36973,7 +36973,7 @@
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
@@ -37087,7 +37087,7 @@
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1679" t="inlineStr">
@@ -37133,7 +37133,7 @@
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1681" t="inlineStr">
@@ -37390,7 +37390,7 @@
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1692" t="inlineStr">
@@ -37805,7 +37805,7 @@
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1709" t="inlineStr">
@@ -38159,7 +38159,7 @@
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1723" t="inlineStr">
@@ -38278,7 +38278,7 @@
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1728" t="inlineStr">
@@ -38366,7 +38366,7 @@
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1732" t="inlineStr">
@@ -38442,7 +38442,7 @@
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1736" t="inlineStr">
@@ -38480,7 +38480,7 @@
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1738" t="inlineStr">
@@ -38499,7 +38499,7 @@
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1739" t="inlineStr">
@@ -38613,7 +38613,7 @@
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1745" t="inlineStr">
@@ -38632,7 +38632,7 @@
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1746" t="inlineStr">
@@ -38651,7 +38651,7 @@
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1747" t="inlineStr">
@@ -38727,7 +38727,7 @@
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1751" t="inlineStr">
@@ -38765,7 +38765,7 @@
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1753" t="inlineStr">
@@ -38784,7 +38784,7 @@
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1754" t="inlineStr">
@@ -38868,7 +38868,7 @@
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1758" t="inlineStr">
@@ -39094,7 +39094,7 @@
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1768" t="inlineStr">
@@ -39113,7 +39113,7 @@
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1769" t="inlineStr">
@@ -39505,7 +39505,7 @@
     <row r="1785">
       <c r="A1785" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1785" t="inlineStr">
@@ -39777,7 +39777,7 @@
     <row r="1797">
       <c r="A1797" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1797" t="inlineStr">
@@ -39815,7 +39815,7 @@
     <row r="1799">
       <c r="A1799" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1799" t="inlineStr">
@@ -39834,7 +39834,7 @@
     <row r="1800">
       <c r="A1800" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1800" t="inlineStr">
@@ -39872,7 +39872,7 @@
     <row r="1802">
       <c r="A1802" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1802" t="inlineStr">
@@ -39891,7 +39891,7 @@
     <row r="1803">
       <c r="A1803" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1803" t="inlineStr">
@@ -39929,7 +39929,7 @@
     <row r="1805">
       <c r="A1805" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1805" t="inlineStr">
@@ -39986,7 +39986,7 @@
     <row r="1808">
       <c r="A1808" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1808" t="inlineStr">
@@ -40081,7 +40081,7 @@
     <row r="1813">
       <c r="A1813" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1813" t="inlineStr">
@@ -40138,7 +40138,7 @@
     <row r="1816">
       <c r="A1816" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1816" t="inlineStr">
@@ -40157,7 +40157,7 @@
     <row r="1817">
       <c r="A1817" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1817" t="inlineStr">
@@ -40314,7 +40314,7 @@
     <row r="1824">
       <c r="A1824" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1824" t="inlineStr">
@@ -40371,7 +40371,7 @@
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="B1827" t="inlineStr">
@@ -40530,7 +40530,7 @@
     <row r="1836">
       <c r="A1836" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1836" t="inlineStr">
@@ -40549,7 +40549,7 @@
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1837" t="inlineStr">
@@ -40568,7 +40568,7 @@
     <row r="1838">
       <c r="A1838" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1838" t="inlineStr">
@@ -40587,7 +40587,7 @@
     <row r="1839">
       <c r="A1839" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1839" t="inlineStr">
@@ -40606,7 +40606,7 @@
     <row r="1840">
       <c r="A1840" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1840" t="inlineStr">
@@ -40625,7 +40625,7 @@
     <row r="1841">
       <c r="A1841" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1841" t="inlineStr">
@@ -40644,7 +40644,7 @@
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1842" t="inlineStr">
@@ -40728,7 +40728,7 @@
     <row r="1846">
       <c r="A1846" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1846" t="inlineStr">
@@ -40747,7 +40747,7 @@
     <row r="1847">
       <c r="A1847" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1847" t="inlineStr">
@@ -41084,7 +41084,7 @@
     <row r="1862">
       <c r="A1862" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1862" t="inlineStr">
@@ -41218,7 +41218,7 @@
     <row r="1868">
       <c r="A1868" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1868" t="inlineStr">
@@ -41421,7 +41421,7 @@
     <row r="1877">
       <c r="A1877" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1877" t="inlineStr">
@@ -41509,7 +41509,7 @@
     <row r="1881">
       <c r="A1881" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1881" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="1882">
       <c r="A1882" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1882" t="inlineStr">
@@ -41589,7 +41589,7 @@
     <row r="1885">
       <c r="A1885" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1885" t="inlineStr">
@@ -41719,7 +41719,7 @@
     <row r="1891">
       <c r="A1891" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1891" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="1892">
       <c r="A1892" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1892" t="inlineStr">
@@ -41960,7 +41960,7 @@
     <row r="1902">
       <c r="A1902" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1902" t="inlineStr">
@@ -41979,7 +41979,7 @@
     <row r="1903">
       <c r="A1903" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1903" t="inlineStr">
@@ -42021,7 +42021,7 @@
     <row r="1905">
       <c r="A1905" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1905" t="inlineStr">
@@ -42040,7 +42040,7 @@
     <row r="1906">
       <c r="A1906" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1906" t="inlineStr">
@@ -42059,7 +42059,7 @@
     <row r="1907">
       <c r="A1907" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1907" t="inlineStr">
@@ -42304,7 +42304,7 @@
     <row r="1918">
       <c r="A1918" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1918" t="inlineStr">
@@ -42323,7 +42323,7 @@
     <row r="1919">
       <c r="A1919" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1919" t="inlineStr">
@@ -42361,7 +42361,7 @@
     <row r="1921">
       <c r="A1921" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1921" t="inlineStr">
@@ -42426,7 +42426,7 @@
     <row r="1924">
       <c r="A1924" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1924" t="inlineStr">
@@ -42468,7 +42468,7 @@
     <row r="1926">
       <c r="A1926" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1926" t="inlineStr">
@@ -42579,7 +42579,7 @@
     <row r="1931">
       <c r="A1931" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1931" t="inlineStr">
@@ -42644,7 +42644,7 @@
     <row r="1934">
       <c r="A1934" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1934" t="inlineStr">
@@ -42663,7 +42663,7 @@
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1935" t="inlineStr">
@@ -42797,7 +42797,7 @@
     <row r="1941">
       <c r="A1941" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1941" t="inlineStr">
@@ -42900,7 +42900,7 @@
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1946" t="inlineStr">
@@ -43172,7 +43172,7 @@
     <row r="1958">
       <c r="A1958" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1958" t="inlineStr">
@@ -43306,7 +43306,7 @@
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr">
@@ -43325,7 +43325,7 @@
     <row r="1965">
       <c r="A1965" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1965" t="inlineStr">
@@ -43344,7 +43344,7 @@
     <row r="1966">
       <c r="A1966" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1966" t="inlineStr">
@@ -43535,7 +43535,7 @@
     <row r="1975">
       <c r="A1975" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1975" t="inlineStr">
@@ -43554,7 +43554,7 @@
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1976" t="inlineStr">
@@ -43573,7 +43573,7 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1977" t="inlineStr">
@@ -43684,7 +43684,7 @@
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1982" t="inlineStr">
@@ -43749,7 +43749,7 @@
     <row r="1985">
       <c r="A1985" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1985" t="inlineStr">
@@ -43814,7 +43814,7 @@
     <row r="1988">
       <c r="A1988" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1988" t="inlineStr">
@@ -43852,7 +43852,7 @@
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1990" t="inlineStr">
@@ -43913,7 +43913,7 @@
     <row r="1993">
       <c r="A1993" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1993" t="inlineStr">
@@ -43932,7 +43932,7 @@
     <row r="1994">
       <c r="A1994" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1994" t="inlineStr">
@@ -43951,7 +43951,7 @@
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr">
@@ -43970,7 +43970,7 @@
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1996" t="inlineStr">
@@ -43989,7 +43989,7 @@
     <row r="1997">
       <c r="A1997" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B1997" t="inlineStr">
@@ -44096,7 +44096,7 @@
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2002" t="inlineStr">
@@ -44253,7 +44253,7 @@
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr">
@@ -44272,7 +44272,7 @@
     <row r="2010">
       <c r="A2010" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2010" t="inlineStr">
@@ -44452,7 +44452,7 @@
     <row r="2018">
       <c r="A2018" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2018" t="inlineStr">
@@ -44540,7 +44540,7 @@
     <row r="2022">
       <c r="A2022" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2022" t="inlineStr">
@@ -44559,7 +44559,7 @@
     <row r="2023">
       <c r="A2023" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2023" t="inlineStr">
@@ -44578,7 +44578,7 @@
     <row r="2024">
       <c r="A2024" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2024" t="inlineStr">
@@ -44984,7 +44984,7 @@
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2042" t="inlineStr">
@@ -45041,7 +45041,7 @@
     <row r="2045">
       <c r="A2045" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2045" t="inlineStr">
@@ -45060,7 +45060,7 @@
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2046" t="inlineStr">
@@ -45263,7 +45263,7 @@
     <row r="2055">
       <c r="A2055" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2055" t="inlineStr">
@@ -45282,7 +45282,7 @@
     <row r="2056">
       <c r="A2056" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2056" t="inlineStr">
@@ -45324,7 +45324,7 @@
     <row r="2058">
       <c r="A2058" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2058" t="inlineStr">
@@ -45389,7 +45389,7 @@
     <row r="2061">
       <c r="A2061" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2061" t="inlineStr">
@@ -45408,7 +45408,7 @@
     <row r="2062">
       <c r="A2062" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2062" t="inlineStr">
@@ -45450,7 +45450,7 @@
     <row r="2064">
       <c r="A2064" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2064" t="inlineStr">
@@ -45469,7 +45469,7 @@
     <row r="2065">
       <c r="A2065" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2065" t="inlineStr">
@@ -45511,7 +45511,7 @@
     <row r="2067">
       <c r="A2067" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2067" t="inlineStr">
@@ -45683,7 +45683,7 @@
     <row r="2075">
       <c r="A2075" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2075" t="inlineStr">
@@ -45748,7 +45748,7 @@
     <row r="2078">
       <c r="A2078" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2078" t="inlineStr">
@@ -45790,7 +45790,7 @@
     <row r="2080">
       <c r="A2080" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2080" t="inlineStr">
@@ -45970,7 +45970,7 @@
     <row r="2088">
       <c r="A2088" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2088" t="inlineStr">
@@ -46058,7 +46058,7 @@
     <row r="2092">
       <c r="A2092" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2092" t="inlineStr">
@@ -46119,7 +46119,7 @@
     <row r="2095">
       <c r="A2095" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2095" t="inlineStr">
@@ -46138,7 +46138,7 @@
     <row r="2096">
       <c r="A2096" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2096" t="inlineStr">
@@ -46157,7 +46157,7 @@
     <row r="2097">
       <c r="A2097" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2097" t="inlineStr">
@@ -46176,7 +46176,7 @@
     <row r="2098">
       <c r="A2098" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2098" t="inlineStr">
@@ -46264,7 +46264,7 @@
     <row r="2102">
       <c r="A2102" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2102" t="inlineStr">
@@ -46398,7 +46398,7 @@
     <row r="2108">
       <c r="A2108" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2108" t="inlineStr">
@@ -46463,7 +46463,7 @@
     <row r="2111">
       <c r="A2111" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2111" t="inlineStr">
@@ -46482,7 +46482,7 @@
     <row r="2112">
       <c r="A2112" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2112" t="inlineStr">
@@ -46543,7 +46543,7 @@
     <row r="2115">
       <c r="A2115" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2115" t="inlineStr">
@@ -46673,7 +46673,7 @@
     <row r="2121">
       <c r="A2121" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2121" t="inlineStr">
@@ -46933,7 +46933,7 @@
     <row r="2133">
       <c r="A2133" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2133" t="inlineStr">
@@ -46975,7 +46975,7 @@
     <row r="2135">
       <c r="A2135" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2135" t="inlineStr">
@@ -47132,7 +47132,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
@@ -47151,7 +47151,7 @@
     <row r="2143">
       <c r="A2143" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2143" t="inlineStr">
@@ -47239,7 +47239,7 @@
     <row r="2147">
       <c r="A2147" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2147" t="inlineStr">
@@ -47258,7 +47258,7 @@
     <row r="2148">
       <c r="A2148" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2148" t="inlineStr">
@@ -47277,7 +47277,7 @@
     <row r="2149">
       <c r="A2149" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2149" t="inlineStr">
@@ -47315,7 +47315,7 @@
     <row r="2151">
       <c r="A2151" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2151" t="inlineStr">
@@ -47357,7 +47357,7 @@
     <row r="2153">
       <c r="A2153" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2153" t="inlineStr">
@@ -47376,7 +47376,7 @@
     <row r="2154">
       <c r="A2154" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2154" t="inlineStr">
@@ -47395,7 +47395,7 @@
     <row r="2155">
       <c r="A2155" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2155" t="inlineStr">
@@ -47414,7 +47414,7 @@
     <row r="2156">
       <c r="A2156" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2156" t="inlineStr">
@@ -47494,7 +47494,7 @@
     <row r="2160">
       <c r="A2160" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2160" t="inlineStr">
@@ -47513,7 +47513,7 @@
     <row r="2161">
       <c r="A2161" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2161" t="inlineStr">
@@ -47532,7 +47532,7 @@
     <row r="2162">
       <c r="A2162" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2162" t="inlineStr">
@@ -47551,7 +47551,7 @@
     <row r="2163">
       <c r="A2163" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2163" t="inlineStr">
@@ -47593,7 +47593,7 @@
     <row r="2165">
       <c r="A2165" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2165" t="inlineStr">
@@ -47681,7 +47681,7 @@
     <row r="2169">
       <c r="A2169" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2169" t="inlineStr">
@@ -47700,7 +47700,7 @@
     <row r="2170">
       <c r="A2170" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2170" t="inlineStr">
@@ -47811,7 +47811,7 @@
     <row r="2175">
       <c r="A2175" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2175" t="inlineStr">
@@ -47918,7 +47918,7 @@
     <row r="2180">
       <c r="A2180" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2180" t="inlineStr">
@@ -47937,7 +47937,7 @@
     <row r="2181">
       <c r="A2181" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2181" t="inlineStr">
@@ -47998,7 +47998,7 @@
     <row r="2184">
       <c r="A2184" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2184" t="inlineStr">
@@ -48017,7 +48017,7 @@
     <row r="2185">
       <c r="A2185" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2185" t="inlineStr">
@@ -48082,7 +48082,7 @@
     <row r="2188">
       <c r="A2188" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2188" t="inlineStr">
@@ -48101,7 +48101,7 @@
     <row r="2189">
       <c r="A2189" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2189" t="inlineStr">
@@ -48143,7 +48143,7 @@
     <row r="2191">
       <c r="A2191" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2191" t="inlineStr">
@@ -48231,7 +48231,7 @@
     <row r="2195">
       <c r="A2195" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2195" t="inlineStr">
@@ -48250,7 +48250,7 @@
     <row r="2196">
       <c r="A2196" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2196" t="inlineStr">
@@ -48269,7 +48269,7 @@
     <row r="2197">
       <c r="A2197" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2197" t="inlineStr">
@@ -48288,7 +48288,7 @@
     <row r="2198">
       <c r="A2198" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2198" t="inlineStr">
@@ -48326,7 +48326,7 @@
     <row r="2200">
       <c r="A2200" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2200" t="inlineStr">
@@ -48368,7 +48368,7 @@
     <row r="2202">
       <c r="A2202" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2202" t="inlineStr">
@@ -48433,7 +48433,7 @@
     <row r="2205">
       <c r="A2205" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2205" t="inlineStr">
@@ -48517,7 +48517,7 @@
     <row r="2209">
       <c r="A2209" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2209" t="inlineStr">
@@ -48559,7 +48559,7 @@
     <row r="2211">
       <c r="A2211" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2211" t="inlineStr">
@@ -48601,7 +48601,7 @@
     <row r="2213">
       <c r="A2213" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2213" t="inlineStr">
@@ -48620,7 +48620,7 @@
     <row r="2214">
       <c r="A2214" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2214" t="inlineStr">
@@ -48662,7 +48662,7 @@
     <row r="2216">
       <c r="A2216" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2216" t="inlineStr">
@@ -48704,7 +48704,7 @@
     <row r="2218">
       <c r="A2218" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2218" t="inlineStr">
@@ -48746,7 +48746,7 @@
     <row r="2220">
       <c r="A2220" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2220" t="inlineStr">
@@ -48765,7 +48765,7 @@
     <row r="2221">
       <c r="A2221" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2221" t="inlineStr">
@@ -48784,7 +48784,7 @@
     <row r="2222">
       <c r="A2222" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2222" t="inlineStr">
@@ -48803,7 +48803,7 @@
     <row r="2223">
       <c r="A2223" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2223" t="inlineStr">
@@ -48891,7 +48891,7 @@
     <row r="2227">
       <c r="A2227" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2227" t="inlineStr">
@@ -48910,7 +48910,7 @@
     <row r="2228">
       <c r="A2228" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2228" t="inlineStr">
@@ -48975,7 +48975,7 @@
     <row r="2231">
       <c r="A2231" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2231" t="inlineStr">
@@ -49017,7 +49017,7 @@
     <row r="2233">
       <c r="A2233" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2233" t="inlineStr">
@@ -49059,7 +49059,7 @@
     <row r="2235">
       <c r="A2235" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2235" t="inlineStr">
@@ -49101,7 +49101,7 @@
     <row r="2237">
       <c r="A2237" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2237" t="inlineStr">
@@ -49185,7 +49185,7 @@
     <row r="2241">
       <c r="A2241" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2241" t="inlineStr">
@@ -49227,7 +49227,7 @@
     <row r="2243">
       <c r="A2243" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2243" t="inlineStr">
@@ -49384,7 +49384,7 @@
     <row r="2250">
       <c r="A2250" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2250" t="inlineStr">
@@ -49403,7 +49403,7 @@
     <row r="2251">
       <c r="A2251" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2251" t="inlineStr">
@@ -49422,7 +49422,7 @@
     <row r="2252">
       <c r="A2252" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2252" t="inlineStr">
@@ -49487,7 +49487,7 @@
     <row r="2255">
       <c r="A2255" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2255" t="inlineStr">
@@ -49529,7 +49529,7 @@
     <row r="2257">
       <c r="A2257" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2257" t="inlineStr">
@@ -49548,7 +49548,7 @@
     <row r="2258">
       <c r="A2258" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2258" t="inlineStr">
@@ -49567,7 +49567,7 @@
     <row r="2259">
       <c r="A2259" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2259" t="inlineStr">
@@ -49586,7 +49586,7 @@
     <row r="2260">
       <c r="A2260" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2260" t="inlineStr">
@@ -49605,7 +49605,7 @@
     <row r="2261">
       <c r="A2261" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2261" t="inlineStr">
@@ -49647,7 +49647,7 @@
     <row r="2263">
       <c r="A2263" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2263" t="inlineStr">
@@ -49846,7 +49846,7 @@
     <row r="2272">
       <c r="A2272" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2272" t="inlineStr">
@@ -49930,7 +49930,7 @@
     <row r="2276">
       <c r="A2276" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2276" t="inlineStr">
@@ -49972,7 +49972,7 @@
     <row r="2278">
       <c r="A2278" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2278" t="inlineStr">
@@ -50014,7 +50014,7 @@
     <row r="2280">
       <c r="A2280" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2280" t="inlineStr">
@@ -50171,7 +50171,7 @@
     <row r="2287">
       <c r="A2287" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2287" t="inlineStr">
@@ -50236,7 +50236,7 @@
     <row r="2290">
       <c r="A2290" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2290" t="inlineStr">
@@ -50255,7 +50255,7 @@
     <row r="2291">
       <c r="A2291" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2291" t="inlineStr">
@@ -50274,7 +50274,7 @@
     <row r="2292">
       <c r="A2292" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2292" t="inlineStr">
@@ -50293,7 +50293,7 @@
     <row r="2293">
       <c r="A2293" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2293" t="inlineStr">
@@ -50335,7 +50335,7 @@
     <row r="2295">
       <c r="A2295" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2295" t="inlineStr">
@@ -50354,7 +50354,7 @@
     <row r="2296">
       <c r="A2296" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2296" t="inlineStr">
@@ -50373,7 +50373,7 @@
     <row r="2297">
       <c r="A2297" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2297" t="inlineStr">
@@ -50622,7 +50622,7 @@
     <row r="2308">
       <c r="A2308" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2308" t="inlineStr">
@@ -50641,7 +50641,7 @@
     <row r="2309">
       <c r="A2309" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2309" t="inlineStr">
@@ -50702,7 +50702,7 @@
     <row r="2312">
       <c r="A2312" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2312" t="inlineStr">
@@ -50813,7 +50813,7 @@
     <row r="2317">
       <c r="A2317" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2317" t="inlineStr">
@@ -50855,7 +50855,7 @@
     <row r="2319">
       <c r="A2319" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2319" t="inlineStr">
@@ -50874,7 +50874,7 @@
     <row r="2320">
       <c r="A2320" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2320" t="inlineStr">
@@ -50893,7 +50893,7 @@
     <row r="2321">
       <c r="A2321" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2321" t="inlineStr">
@@ -51046,7 +51046,7 @@
     <row r="2328">
       <c r="A2328" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2328" t="inlineStr">
@@ -51088,7 +51088,7 @@
     <row r="2330">
       <c r="A2330" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2330" t="inlineStr">
@@ -51199,7 +51199,7 @@
     <row r="2335">
       <c r="A2335" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2335" t="inlineStr">
@@ -51264,7 +51264,7 @@
     <row r="2338">
       <c r="A2338" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2338" t="inlineStr">
@@ -51283,7 +51283,7 @@
     <row r="2339">
       <c r="A2339" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2339" t="inlineStr">
@@ -51302,7 +51302,7 @@
     <row r="2340">
       <c r="A2340" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2340" t="inlineStr">
@@ -51344,7 +51344,7 @@
     <row r="2342">
       <c r="A2342" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2342" t="inlineStr">
@@ -51363,7 +51363,7 @@
     <row r="2343">
       <c r="A2343" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2343" t="inlineStr">
@@ -51382,7 +51382,7 @@
     <row r="2344">
       <c r="A2344" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2344" t="inlineStr">
@@ -51401,7 +51401,7 @@
     <row r="2345">
       <c r="A2345" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2345" t="inlineStr">
@@ -51420,7 +51420,7 @@
     <row r="2346">
       <c r="A2346" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2346" t="inlineStr">
@@ -51439,7 +51439,7 @@
     <row r="2347">
       <c r="A2347" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2347" t="inlineStr">
@@ -51519,7 +51519,7 @@
     <row r="2351">
       <c r="A2351" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2351" t="inlineStr">
@@ -51584,7 +51584,7 @@
     <row r="2354">
       <c r="A2354" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2354" t="inlineStr">
@@ -51695,7 +51695,7 @@
     <row r="2359">
       <c r="A2359" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2359" t="inlineStr">
@@ -51737,7 +51737,7 @@
     <row r="2361">
       <c r="A2361" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2361" t="inlineStr">
@@ -51756,7 +51756,7 @@
     <row r="2362">
       <c r="A2362" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2362" t="inlineStr">
@@ -51775,7 +51775,7 @@
     <row r="2363">
       <c r="A2363" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2363" t="inlineStr">
@@ -52001,7 +52001,7 @@
     <row r="2373">
       <c r="A2373" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2373" t="inlineStr">
@@ -52066,7 +52066,7 @@
     <row r="2376">
       <c r="A2376" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2376" t="inlineStr">
@@ -52085,7 +52085,7 @@
     <row r="2377">
       <c r="A2377" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2377" t="inlineStr">
@@ -52104,7 +52104,7 @@
     <row r="2378">
       <c r="A2378" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2378" t="inlineStr">
@@ -52146,7 +52146,7 @@
     <row r="2380">
       <c r="A2380" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2380" t="inlineStr">
@@ -52326,7 +52326,7 @@
     <row r="2388">
       <c r="A2388" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2388" t="inlineStr">
@@ -52387,7 +52387,7 @@
     <row r="2391">
       <c r="A2391" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2391" t="inlineStr">
@@ -52544,7 +52544,7 @@
     <row r="2398">
       <c r="A2398" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2398" t="inlineStr">
@@ -52563,7 +52563,7 @@
     <row r="2399">
       <c r="A2399" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2399" t="inlineStr">
@@ -52628,7 +52628,7 @@
     <row r="2402">
       <c r="A2402" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2402" t="inlineStr">
@@ -52942,7 +52942,7 @@
     <row r="2416">
       <c r="A2416" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2416" t="inlineStr">
@@ -52984,7 +52984,7 @@
     <row r="2418">
       <c r="A2418" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2418" t="inlineStr">
@@ -53164,7 +53164,7 @@
     <row r="2426">
       <c r="A2426" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2426" t="inlineStr">
@@ -53455,7 +53455,7 @@
     <row r="2439">
       <c r="A2439" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2439" t="inlineStr">
@@ -53520,7 +53520,7 @@
     <row r="2442">
       <c r="A2442" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2442" t="inlineStr">
@@ -53539,7 +53539,7 @@
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2443" t="inlineStr">
@@ -53558,7 +53558,7 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2444" t="inlineStr">
@@ -53577,7 +53577,7 @@
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2445" t="inlineStr">
@@ -53596,7 +53596,7 @@
     <row r="2446">
       <c r="A2446" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2446" t="inlineStr">
@@ -53615,7 +53615,7 @@
     <row r="2447">
       <c r="A2447" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2447" t="inlineStr">
@@ -53714,7 +53714,7 @@
     <row r="2452">
       <c r="A2452" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2452" t="inlineStr">
@@ -53733,7 +53733,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr">
@@ -53752,7 +53752,7 @@
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2454" t="inlineStr">
@@ -53836,7 +53836,7 @@
     <row r="2458">
       <c r="A2458" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2458" t="inlineStr">
@@ -53855,7 +53855,7 @@
     <row r="2459">
       <c r="A2459" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2459" t="inlineStr">
@@ -53989,7 +53989,7 @@
     <row r="2465">
       <c r="A2465" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2465" t="inlineStr">
@@ -54165,7 +54165,7 @@
     <row r="2473">
       <c r="A2473" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2473" t="inlineStr">
@@ -54253,7 +54253,7 @@
     <row r="2477">
       <c r="A2477" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2477" t="inlineStr">
@@ -54272,7 +54272,7 @@
     <row r="2478">
       <c r="A2478" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2478" t="inlineStr">
@@ -54291,7 +54291,7 @@
     <row r="2479">
       <c r="A2479" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2479" t="inlineStr">
@@ -54310,7 +54310,7 @@
     <row r="2480">
       <c r="A2480" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2480" t="inlineStr">
@@ -54375,7 +54375,7 @@
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2483" t="inlineStr">
@@ -54509,7 +54509,7 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2489" t="inlineStr">
@@ -54528,7 +54528,7 @@
     <row r="2490">
       <c r="A2490" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2490" t="inlineStr">
@@ -54547,7 +54547,7 @@
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2491" t="inlineStr">
@@ -54566,7 +54566,7 @@
     <row r="2492">
       <c r="A2492" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2492" t="inlineStr">
@@ -54811,7 +54811,7 @@
     <row r="2503">
       <c r="A2503" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2503" t="inlineStr">
@@ -54937,7 +54937,7 @@
     <row r="2509">
       <c r="A2509" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2509" t="inlineStr">
@@ -54956,7 +54956,7 @@
     <row r="2510">
       <c r="A2510" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2510" t="inlineStr">
@@ -55197,7 +55197,7 @@
     <row r="2521">
       <c r="A2521" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2521" t="inlineStr">
@@ -55216,7 +55216,7 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2522" t="inlineStr">
@@ -55235,7 +55235,7 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2523" t="inlineStr">
@@ -55277,7 +55277,7 @@
     <row r="2525">
       <c r="A2525" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2525" t="inlineStr">
@@ -55342,7 +55342,7 @@
     <row r="2528">
       <c r="A2528" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2528" t="inlineStr">
@@ -55361,7 +55361,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr">
@@ -55426,7 +55426,7 @@
     <row r="2532">
       <c r="A2532" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2532" t="inlineStr">
@@ -55606,7 +55606,7 @@
     <row r="2540">
       <c r="A2540" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2540" t="inlineStr">
@@ -55625,7 +55625,7 @@
     <row r="2541">
       <c r="A2541" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2541" t="inlineStr">
@@ -55736,7 +55736,7 @@
     <row r="2546">
       <c r="A2546" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2546" t="inlineStr">
@@ -55755,7 +55755,7 @@
     <row r="2547">
       <c r="A2547" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2547" t="inlineStr">
@@ -55774,7 +55774,7 @@
     <row r="2548">
       <c r="A2548" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2548" t="inlineStr">
@@ -55816,7 +55816,7 @@
     <row r="2550">
       <c r="A2550" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2550" t="inlineStr">
@@ -55858,7 +55858,7 @@
     <row r="2552">
       <c r="A2552" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2552" t="inlineStr">
@@ -55877,7 +55877,7 @@
     <row r="2553">
       <c r="A2553" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2553" t="inlineStr">
@@ -55896,7 +55896,7 @@
     <row r="2554">
       <c r="A2554" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2554" t="inlineStr">
@@ -55915,7 +55915,7 @@
     <row r="2555">
       <c r="A2555" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2555" t="inlineStr">
@@ -56072,7 +56072,7 @@
     <row r="2562">
       <c r="A2562" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2562" t="inlineStr">
@@ -56160,7 +56160,7 @@
     <row r="2566">
       <c r="A2566" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2566" t="inlineStr">
@@ -56179,7 +56179,7 @@
     <row r="2567">
       <c r="A2567" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2567" t="inlineStr">
@@ -56217,7 +56217,7 @@
     <row r="2569">
       <c r="A2569" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2569" t="inlineStr">
@@ -56347,7 +56347,7 @@
     <row r="2575">
       <c r="A2575" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2575" t="inlineStr">
@@ -56412,7 +56412,7 @@
     <row r="2578">
       <c r="A2578" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2578" t="inlineStr">
@@ -56496,7 +56496,7 @@
     <row r="2582">
       <c r="A2582" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2582" t="inlineStr">
@@ -56580,7 +56580,7 @@
     <row r="2586">
       <c r="A2586" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2586" t="inlineStr">
@@ -56622,7 +56622,7 @@
     <row r="2588">
       <c r="A2588" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2588" t="inlineStr">
@@ -56641,7 +56641,7 @@
     <row r="2589">
       <c r="A2589" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2589" t="inlineStr">
@@ -56660,7 +56660,7 @@
     <row r="2590">
       <c r="A2590" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2590" t="inlineStr">
@@ -56679,7 +56679,7 @@
     <row r="2591">
       <c r="A2591" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2591" t="inlineStr">
@@ -56717,7 +56717,7 @@
     <row r="2593">
       <c r="A2593" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2593" t="inlineStr">
@@ -56736,7 +56736,7 @@
     <row r="2594">
       <c r="A2594" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2594" t="inlineStr">
@@ -56755,7 +56755,7 @@
     <row r="2595">
       <c r="A2595" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2595" t="inlineStr">
@@ -56793,7 +56793,7 @@
     <row r="2597">
       <c r="A2597" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2597" t="inlineStr">
@@ -56904,7 +56904,7 @@
     <row r="2602">
       <c r="A2602" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2602" t="inlineStr">
@@ -56923,7 +56923,7 @@
     <row r="2603">
       <c r="A2603" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2603" t="inlineStr">
@@ -57122,7 +57122,7 @@
     <row r="2612">
       <c r="A2612" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2612" t="inlineStr">
@@ -57187,7 +57187,7 @@
     <row r="2615">
       <c r="A2615" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2615" t="inlineStr">
@@ -57252,7 +57252,7 @@
     <row r="2618">
       <c r="A2618" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2618" t="inlineStr">
@@ -57294,7 +57294,7 @@
     <row r="2620">
       <c r="A2620" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2620" t="inlineStr">
@@ -57382,7 +57382,7 @@
     <row r="2624">
       <c r="A2624" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2624" t="inlineStr">
@@ -57401,7 +57401,7 @@
     <row r="2625">
       <c r="A2625" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2625" t="inlineStr">
@@ -57512,7 +57512,7 @@
     <row r="2630">
       <c r="A2630" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2630" t="inlineStr">
@@ -57531,7 +57531,7 @@
     <row r="2631">
       <c r="A2631" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2631" t="inlineStr">
@@ -57596,7 +57596,7 @@
     <row r="2634">
       <c r="A2634" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2634" t="inlineStr">
@@ -57684,7 +57684,7 @@
     <row r="2638">
       <c r="A2638" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2638" t="inlineStr">
@@ -57837,7 +57837,7 @@
     <row r="2645">
       <c r="A2645" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2645" t="inlineStr">
@@ -57948,7 +57948,7 @@
     <row r="2650">
       <c r="A2650" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2650" t="inlineStr">
@@ -58151,7 +58151,7 @@
     <row r="2659">
       <c r="A2659" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2659" t="inlineStr">
@@ -58350,7 +58350,7 @@
     <row r="2668">
       <c r="A2668" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2668" t="inlineStr">
@@ -58530,7 +58530,7 @@
     <row r="2676">
       <c r="A2676" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2676" t="inlineStr">
@@ -58618,7 +58618,7 @@
     <row r="2680">
       <c r="A2680" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2680" t="inlineStr">
@@ -58729,7 +58729,7 @@
     <row r="2685">
       <c r="A2685" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2685" t="inlineStr">
@@ -58836,7 +58836,7 @@
     <row r="2690">
       <c r="A2690" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2690" t="inlineStr">
@@ -58855,7 +58855,7 @@
     <row r="2691">
       <c r="A2691" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2691" t="inlineStr">
@@ -58874,7 +58874,7 @@
     <row r="2692">
       <c r="A2692" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2692" t="inlineStr">
@@ -58893,7 +58893,7 @@
     <row r="2693">
       <c r="A2693" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2693" t="inlineStr">
@@ -58912,7 +58912,7 @@
     <row r="2694">
       <c r="A2694" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2694" t="inlineStr">
@@ -59176,7 +59176,7 @@
     <row r="2706">
       <c r="A2706" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2706" t="inlineStr">
@@ -59237,7 +59237,7 @@
     <row r="2709">
       <c r="A2709" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2709" t="inlineStr">
@@ -59256,7 +59256,7 @@
     <row r="2710">
       <c r="A2710" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2710" t="inlineStr">
@@ -59432,7 +59432,7 @@
     <row r="2718">
       <c r="A2718" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2718" t="inlineStr">
@@ -59497,7 +59497,7 @@
     <row r="2721">
       <c r="A2721" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2721" t="inlineStr">
@@ -59516,7 +59516,7 @@
     <row r="2722">
       <c r="A2722" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2722" t="inlineStr">
@@ -59577,7 +59577,7 @@
     <row r="2725">
       <c r="A2725" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2725" t="inlineStr">
@@ -59615,7 +59615,7 @@
     <row r="2727">
       <c r="A2727" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2727" t="inlineStr">
@@ -59634,7 +59634,7 @@
     <row r="2728">
       <c r="A2728" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2728" t="inlineStr">
@@ -59741,7 +59741,7 @@
     <row r="2733">
       <c r="A2733" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2733" t="inlineStr">
@@ -59760,7 +59760,7 @@
     <row r="2734">
       <c r="A2734" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2734" t="inlineStr">
@@ -59779,7 +59779,7 @@
     <row r="2735">
       <c r="A2735" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2735" t="inlineStr">
@@ -59798,7 +59798,7 @@
     <row r="2736">
       <c r="A2736" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2736" t="inlineStr">
@@ -59817,7 +59817,7 @@
     <row r="2737">
       <c r="A2737" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2737" t="inlineStr">
@@ -59859,7 +59859,7 @@
     <row r="2739">
       <c r="A2739" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2739" t="inlineStr">
@@ -59901,7 +59901,7 @@
     <row r="2741">
       <c r="A2741" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2741" t="inlineStr">
@@ -59966,7 +59966,7 @@
     <row r="2744">
       <c r="A2744" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2744" t="inlineStr">
@@ -60008,7 +60008,7 @@
     <row r="2746">
       <c r="A2746" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2746" t="inlineStr">
@@ -60027,7 +60027,7 @@
     <row r="2747">
       <c r="A2747" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2747" t="inlineStr">
@@ -60318,7 +60318,7 @@
     <row r="2760">
       <c r="A2760" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2760" t="inlineStr">
@@ -60586,7 +60586,7 @@
     <row r="2772">
       <c r="A2772" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2772" t="inlineStr">
@@ -60605,7 +60605,7 @@
     <row r="2773">
       <c r="A2773" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2773" t="inlineStr">
@@ -60624,7 +60624,7 @@
     <row r="2774">
       <c r="A2774" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2774" t="inlineStr">
@@ -60662,7 +60662,7 @@
     <row r="2776">
       <c r="A2776" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2776" t="inlineStr">
@@ -60704,7 +60704,7 @@
     <row r="2778">
       <c r="A2778" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2778" t="inlineStr">
@@ -60792,7 +60792,7 @@
     <row r="2782">
       <c r="A2782" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2782" t="inlineStr">
@@ -60857,7 +60857,7 @@
     <row r="2785">
       <c r="A2785" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2785" t="inlineStr">
@@ -60899,7 +60899,7 @@
     <row r="2787">
       <c r="A2787" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2787" t="inlineStr">
@@ -60941,7 +60941,7 @@
     <row r="2789">
       <c r="A2789" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2789" t="inlineStr">
@@ -60960,7 +60960,7 @@
     <row r="2790">
       <c r="A2790" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2790" t="inlineStr">
@@ -60979,7 +60979,7 @@
     <row r="2791">
       <c r="A2791" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2791" t="inlineStr">
@@ -61021,7 +61021,7 @@
     <row r="2793">
       <c r="A2793" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2793" t="inlineStr">
@@ -61105,7 +61105,7 @@
     <row r="2797">
       <c r="A2797" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2797" t="inlineStr">
@@ -61170,7 +61170,7 @@
     <row r="2800">
       <c r="A2800" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2800" t="inlineStr">
@@ -61189,7 +61189,7 @@
     <row r="2801">
       <c r="A2801" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2801" t="inlineStr">
@@ -61231,7 +61231,7 @@
     <row r="2803">
       <c r="A2803" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2803" t="inlineStr">
@@ -61273,7 +61273,7 @@
     <row r="2805">
       <c r="A2805" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2805" t="inlineStr">
@@ -61315,7 +61315,7 @@
     <row r="2807">
       <c r="A2807" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2807" t="inlineStr">
@@ -61460,7 +61460,7 @@
     <row r="2814">
       <c r="A2814" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2814" t="inlineStr">
@@ -61613,7 +61613,7 @@
     <row r="2821">
       <c r="A2821" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2821" t="inlineStr">
@@ -61632,7 +61632,7 @@
     <row r="2822">
       <c r="A2822" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2822" t="inlineStr">
@@ -61651,7 +61651,7 @@
     <row r="2823">
       <c r="A2823" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2823" t="inlineStr">
@@ -61689,7 +61689,7 @@
     <row r="2825">
       <c r="A2825" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2825" t="inlineStr">
@@ -61708,7 +61708,7 @@
     <row r="2826">
       <c r="A2826" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2826" t="inlineStr">
@@ -61792,7 +61792,7 @@
     <row r="2830">
       <c r="A2830" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2830" t="inlineStr">
@@ -61949,7 +61949,7 @@
     <row r="2837">
       <c r="A2837" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2837" t="inlineStr">
@@ -61968,7 +61968,7 @@
     <row r="2838">
       <c r="A2838" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2838" t="inlineStr">
@@ -62010,7 +62010,7 @@
     <row r="2840">
       <c r="A2840" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2840" t="inlineStr">
@@ -62029,7 +62029,7 @@
     <row r="2841">
       <c r="A2841" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2841" t="inlineStr">
@@ -62048,7 +62048,7 @@
     <row r="2842">
       <c r="A2842" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2842" t="inlineStr">
@@ -62067,7 +62067,7 @@
     <row r="2843">
       <c r="A2843" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2843" t="inlineStr">
@@ -62293,7 +62293,7 @@
     <row r="2853">
       <c r="A2853" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2853" t="inlineStr">
@@ -62515,7 +62515,7 @@
     <row r="2863">
       <c r="A2863" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B2863" t="inlineStr">
@@ -62597,6 +62597,29 @@
       <c r="E2866" t="inlineStr">
         <is>
           <t>FCamara</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>André Levi Neri Longo</t>
+        </is>
+      </c>
+      <c r="C2867" t="inlineStr">
+        <is>
+          <t>50000469</t>
+        </is>
+      </c>
+      <c r="D2867" t="inlineStr"/>
+      <c r="E2867" t="inlineStr">
+        <is>
+          <t>NextGen</t>
         </is>
       </c>
     </row>
